--- a/beispiele/malters/ergebnis/Geschwister_zwingend/stammdaten.xlsx
+++ b/beispiele/malters/ergebnis/Geschwister_zwingend/stammdaten.xlsx
@@ -28,7 +28,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Foerderangebote'!$A$1:$L$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Stundentafel'!$A$1:$L$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Kinder'!$A$1:$W$885</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Einstellungen'!$A$1:$B$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Einstellungen'!$A$1:$B$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -526,7 +526,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -918,19 +918,48 @@
           <t>planung</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>wachstum_prozent: 3</t>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>wachstum_prozent: 3
+vollpensum_lektionen: 28
+austritt_prozent:
+  '6': 10
+quartiere:
+- name: Neubaugebiet Nord
+  schulhaus: Bündtmättli
+  ab: 2029/30
+  wohnungen: 120
+  kinder_pro_wohnung: 0.3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>kosten</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>annahme: Richtwerte für das Beispiel, nicht die Zahlen der Gemeinde Malters
+lektion_chf: 4000
+raum_chf:
+  Klassenzimmer: 15000
+  Kindergarten: 15000
+  Turnhalle: 45000
+  TTG-Zimmer: 12000
+schulhaus_chf: 90000
+transport_chf_pro_kind: 1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>gewichte</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>schulweg_pro_km: 100
 klasse: 400
@@ -938,8 +967,34 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>_hypothese</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Was wäre, wenn Geschwister immer ins selbe Schulhaus müssen?
+...</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>_ziel</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Qualität
+...</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B14"/>
+  <autoFilter ref="A1:B17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/beispiele/malters/ergebnis/Geschwister_zwingend/stammdaten.xlsx
+++ b/beispiele/malters/ergebnis/Geschwister_zwingend/stammdaten.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>

--- a/beispiele/malters/ergebnis/Geschwister_zwingend/stammdaten.xlsx
+++ b/beispiele/malters/ergebnis/Geschwister_zwingend/stammdaten.xlsx
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Info'!$A$1:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Schulhaeuser'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Schulhaeuser'!$A$1:$H$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Raeume'!$A$1:$F$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Klassentypen'!$A$1:$I$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Faecher'!$A$1:$D$15</definedName>
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>0.1.0</t>
+          <t>0.2.0</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -1005,16 +1005,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1030,25 +1031,30 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>adresse</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>lat</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>lon</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>stufen</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>nicht_verfuegbar</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>nutzt</t>
         </is>
@@ -1065,19 +1071,24 @@
           <t>BM</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Schwarzenbergstrasse 14, 6102 Malters</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
         <v>47.0338</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="E2" s="2" t="n">
         <v>8.186199999999999</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>KG1-6</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1090,19 +1101,24 @@
           <t>EI</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Hellbühlstrasse 52, 6102 Malters</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
         <v>47.0402</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="E3" s="2" t="n">
         <v>8.176500000000001</v>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>KG1-6</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1115,23 +1131,28 @@
           <t>IF</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Naturkindergarten Im Feld, c/o Schulhaus Eischachen, Hellbühlstrasse 52, 6102 Malters</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
         <v>47.0445</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="E4" s="2" t="n">
         <v>8.188000000000001</v>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>KG1-KG2</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Mo-NM;Di-NM;Do-NM;Fr-NM</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1144,22 +1165,27 @@
           <t>OS</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Schulhaus Muoshof, Muoshofstrasse 26, 6102 Malters</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
         <v>47.0372</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="E5" s="2" t="n">
         <v>8.1838</v>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>S1-S3</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:H5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
